--- a/data/examiner_ssm.xlsx
+++ b/data/examiner_ssm.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Yotanut\OneDrive\Desktop\SSM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C95D5665-ABD2-4ABA-A943-F06A84AD3785}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F099AF4-DEC5-47BF-BC37-EAF31499CFE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{F81A2575-5109-49D6-BFE7-C770B4AF63E6}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="65">
   <si>
     <t>ภัสรสุดา</t>
   </si>
@@ -214,6 +214,21 @@
   </si>
   <si>
     <t>floor</t>
+  </si>
+  <si>
+    <t>นัฐชาติ</t>
+  </si>
+  <si>
+    <t>ณัฐกฤตา</t>
+  </si>
+  <si>
+    <t>ลัลน์ลลิต</t>
+  </si>
+  <si>
+    <t>ศุทธินี,พงษ์ศักดิ์</t>
+  </si>
+  <si>
+    <t xml:space="preserve">นภสร </t>
   </si>
 </sst>
 </file>
@@ -566,7 +581,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C09F9EB9-E184-450A-951E-4B7021A71683}">
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:H23"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -1115,6 +1130,58 @@
         <v>51</v>
       </c>
     </row>
+    <row r="22" spans="1:8">
+      <c r="A22">
+        <v>10</v>
+      </c>
+      <c r="B22">
+        <v>1</v>
+      </c>
+      <c r="C22" t="s">
+        <v>60</v>
+      </c>
+      <c r="D22" t="s">
+        <v>61</v>
+      </c>
+      <c r="E22" t="s">
+        <v>62</v>
+      </c>
+      <c r="F22" t="s">
+        <v>63</v>
+      </c>
+      <c r="G22" t="s">
+        <v>64</v>
+      </c>
+      <c r="H22" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
+      <c r="A23">
+        <v>10</v>
+      </c>
+      <c r="B23">
+        <v>2</v>
+      </c>
+      <c r="C23" t="s">
+        <v>60</v>
+      </c>
+      <c r="D23" t="s">
+        <v>61</v>
+      </c>
+      <c r="E23" t="s">
+        <v>62</v>
+      </c>
+      <c r="F23" t="s">
+        <v>63</v>
+      </c>
+      <c r="G23" t="s">
+        <v>64</v>
+      </c>
+      <c r="H23" t="s">
+        <v>51</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
